--- a/output/2026-10-01_23_Malesia_Melaka_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-01_23_Malesia_Melaka_Impiantistica_aspirazione_industriale.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Azienda confermata tramite sito aziendale (pagine 'Factory Exhaust Systems', 'Ventilation System Malaysia'), copertura dichiarata estesa a Melaka tra le altre regioni. Sede fisica non a Melaka: verificare disponibilita' operativa locale.</t>
+          <t>Azienda confermata tramite sito aziendale (pagine 'Factory Exhaust Systems', 'Ventilation System Malaysia'), copertura dichiarata estesa a Melaka tra le altre regioni. Sede fisica non a Melaka: verificare disponibilita' operativa locale. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Azienda confermata, sede a Senai (Johor Bahru). Pagina prodotto del sito cita esplicitamente Melaka tra le aree servite per dust collector. Sede fisica non a Melaka: verificare disponibilita' operativa locale.</t>
+          <t>Azienda confermata, sede a Senai (Johor Bahru). Pagina prodotto del sito cita esplicitamente Melaka tra le aree servite per dust collector. Sede fisica non a Melaka: verificare disponibilita' operativa locale. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">

--- a/output/2026-10-01_23_Malesia_Melaka_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-01_23_Malesia_Melaka_Impiantistica_aspirazione_industriale.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Azienda confermata, sede a Melaka. Prodotti dust collector HITZ e JETMAC e ventilatori industriali confermati su pagine prodotto del sito (alliance-supplies.com / alliancesuppliesonline.com.my). Fonte: sito aziendale, ricerca web.</t>
+          <t>Azienda confermata, sede a Melaka. Prodotti dust collector HITZ e JETMAC e ventilatori industriali confermati su pagine prodotto del sito (alliance-supplies.com / alliancesuppliesonline.com.my). Fonte: sito aziendale, ricerca web. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
